--- a/forms/trg/Formulir_TRG_neuro-onc.xlsx
+++ b/forms/trg/Formulir_TRG_neuro-onc.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Syahrul, S.Kep., Ns., M.Kep., Sp.Kep.MB</t>
+          <t>Dr. Rosyidah Arafat, S.Kep., Ns.,M.Kep., Sp.KMB</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,24 +928,16 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Critical Care Nursing, Cardiovascular Critical, and Chronic disease</t>
+          <t>Neuroscience and palliative care</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-3352-7672</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>57215697991</t>
-        </is>
-      </c>
+      <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Elly Lilianty Sjattar, S.Kp.,M.Kes.</t>
+          <t>Syahrul, S.Kep., Ns., M.Kep., Sp.Kep.MB</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +965,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Cronic disease, Infectious disease, and Selfcare management</t>
+          <t>Critical Care Nursing, Cardiovascular Critical, and Chronic disease</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +974,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7376-5771</t>
+          <t>0000-0002-3352-7672</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57212209382</t>
+          <t>57215697991</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,22 +995,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Lee Wan Ling, , MN.,RN.</t>
+          <t>Prof. Dr. Elly Lilianty Sjattar, S.Kp.,M.Kes.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>(Departement of Nursing, Malaya University, Malaysia)</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Nursing Science</t>
+          <t>Cronic disease, Infectious disease, and Selfcare management</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,13 +1019,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5584-2905</t>
+          <t>0000-0002-7376-5771</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>55957691500</t>
+          <t>57212209382</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,22 +1040,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Gulzar Malik, BScN, BA, MNsg, PhD, FHEA</t>
+          <t>Dr. Lee Wan Ling, , MN.,RN.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>School of Nursing and Midwifery, La Trobe University, Melbourne, Australia</t>
+          <t>(Departement of Nursing, Malaya University, Malaysia)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Acute and critical care nursing</t>
+          <t>Nursing Science</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,11 +1064,15 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1935-1367</t>
+          <t>0000-0002-5584-2905</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>55957691500</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,22 +1085,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Domingos Soares, S.Kep, Ns., MM, M.Enf</t>
+          <t>Gulzar Malik, BScN, BA, MNsg, PhD, FHEA</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Saúde Publica Timor-Leste</t>
+          <t>School of Nursing and Midwifery, La Trobe University, Melbourne, Australia</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Nursing leadership, health systems readiness</t>
+          <t>Acute and critical care nursing</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1113,15 +1109,11 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3466-1267</t>
+          <t>0000-0002-1935-1367</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>57434714200</t>
-        </is>
-      </c>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1134,31 +1126,39 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Indra Gaffar, S.Kep., Ns., M.Kep</t>
+          <t>Dr. Domingos Soares, S.Kep, Ns., MM, M.Enf</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Instituto Nacional de Saúde Publica Timor-Leste</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Patient Safety and Quality in Healthcare</t>
+          <t>Nursing leadership, health systems readiness</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3466-1267</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57434714200</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Andi Nurul Inayah</t>
+          <t>Indra Gaffar, S.Kep., Ns., M.Kep</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Nursing Science</t>
+          <t>Patient Safety and Quality in Healthcare</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1208,22 +1208,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Alif Muhammad Islam</t>
+          <t>Andi Nurul Inayah</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
           <t>Nursing Science</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>NEO-NURS Team</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1243,10 +1243,26 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Alif Muhammad Islam</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Nursing Science</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>NEO-NURS Team</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1254,7 +1270,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1443,15 +1463,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
